--- a/artfynd/A 51465-2019 artfynd.xlsx
+++ b/artfynd/A 51465-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121143624</v>
       </c>
       <c r="B2" t="n">
-        <v>91083</v>
+        <v>91093</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 51465-2019 artfynd.xlsx
+++ b/artfynd/A 51465-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121143624</v>
       </c>
       <c r="B2" t="n">
-        <v>91093</v>
+        <v>91105</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 51465-2019 artfynd.xlsx
+++ b/artfynd/A 51465-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121143624</v>
       </c>
       <c r="B2" t="n">
-        <v>91105</v>
+        <v>91106</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 51465-2019 artfynd.xlsx
+++ b/artfynd/A 51465-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121143624</v>
       </c>
       <c r="B2" t="n">
-        <v>91106</v>
+        <v>91109</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 51465-2019 artfynd.xlsx
+++ b/artfynd/A 51465-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -809,6 +809,118 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122094117</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91294</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>3884</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Hasselticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dichomitus campestris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Månstorp, Månstorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>414872</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6487768</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Götene</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Götene</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Magnus Svensson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Svensson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51465-2019 artfynd.xlsx
+++ b/artfynd/A 51465-2019 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>122094117</v>
       </c>
       <c r="B3" t="n">
-        <v>91294</v>
+        <v>91295</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 51465-2019 artfynd.xlsx
+++ b/artfynd/A 51465-2019 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>122094117</v>
       </c>
       <c r="B3" t="n">
-        <v>91295</v>
+        <v>91304</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 51465-2019 artfynd.xlsx
+++ b/artfynd/A 51465-2019 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>122094117</v>
       </c>
       <c r="B3" t="n">
-        <v>91304</v>
+        <v>91311</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 51465-2019 artfynd.xlsx
+++ b/artfynd/A 51465-2019 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>122094117</v>
       </c>
       <c r="B3" t="n">
-        <v>91311</v>
+        <v>91313</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 51465-2019 artfynd.xlsx
+++ b/artfynd/A 51465-2019 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>122094117</v>
       </c>
       <c r="B3" t="n">
-        <v>91329</v>
+        <v>91339</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 51465-2019 artfynd.xlsx
+++ b/artfynd/A 51465-2019 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>122094117</v>
       </c>
       <c r="B3" t="n">
-        <v>91339</v>
+        <v>91351</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 51465-2019 artfynd.xlsx
+++ b/artfynd/A 51465-2019 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>122094117</v>
       </c>
       <c r="B3" t="n">
-        <v>91351</v>
+        <v>91356</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 51465-2019 artfynd.xlsx
+++ b/artfynd/A 51465-2019 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>122094117</v>
       </c>
       <c r="B3" t="n">
-        <v>91356</v>
+        <v>91361</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,11 +828,6 @@
       </c>
       <c r="E3" t="n">
         <v>3884</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Hasselticka</t>
-        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/artfynd/A 51465-2019 artfynd.xlsx
+++ b/artfynd/A 51465-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -916,6 +916,118 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124154699</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91391</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Månstorp, Månstorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>414904</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6487723</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Götene</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Götene</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Svensson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Svensson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
